--- a/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -85,151 +85,151 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MENDOZA</t>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
+    <t>CERON</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>GALVEZ</t>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>CHIMALHUA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>MORA</t>
   </si>
   <si>
     <t>CARRASCO</t>
   </si>
   <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
     <t>ANETTE</t>
   </si>
   <si>
-    <t>VALERIA</t>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
   </si>
   <si>
     <t>JESUS</t>
   </si>
   <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>SALMA AISHA</t>
   </si>
   <si>
-    <t>ROSA</t>
+    <t>DANIEL ELEAZAR</t>
   </si>
   <si>
     <t>ALEXANDRA</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>FEDERICO ABIMAEL</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
-    <t>ARLETT</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -659,16 +659,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -757,7 +757,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -766,10 +766,10 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="H7">
         <v>8.199999999999999</v>
@@ -825,16 +825,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.55</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -848,16 +851,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -871,16 +877,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -894,16 +903,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>69.77</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -917,16 +929,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>93.75</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -937,19 +952,22 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>92.11</v>
+      </c>
+      <c r="H7">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1005,16 +1023,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.55</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1031,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1066,7 +1084,7 @@
         <v>86.11</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1083,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>72.09</v>
+        <v>69.77</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1109,16 +1127,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>59.38</v>
+        <v>93.75</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1129,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1138,13 +1156,13 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,10 +1210,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1209,22 +1227,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920105</v>
+        <v>22330051920284</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1232,22 +1250,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920122</v>
+        <v>22330051920333</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1255,7 +1273,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920068</v>
+        <v>22330051920053</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1264,7 +1282,7 @@
         <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1278,22 +1296,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920043</v>
+        <v>22330051920061</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1301,22 +1319,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920045</v>
+        <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1324,22 +1342,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920352</v>
+        <v>21330051920053</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1347,114 +1365,114 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920097</v>
+        <v>22330051920084</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920053</v>
+        <v>22330051920189</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920062</v>
+        <v>22330051920043</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920070</v>
+        <v>22330051920352</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920081</v>
+        <v>22330051920173</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1462,22 +1480,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920035</v>
+        <v>22330051920114</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1485,22 +1503,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920036</v>
+        <v>22330051920122</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1508,22 +1526,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920037</v>
+        <v>22330051920157</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1531,22 +1549,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920331</v>
+        <v>22330051920062</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1554,22 +1572,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920327</v>
+        <v>22330051920064</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1577,70 +1595,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920141</v>
+        <v>22330051920081</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920198</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920329</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>Mat</t>
   </si>
@@ -85,90 +85,87 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>CERON</t>
   </si>
   <si>
     <t>AYOHUA</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>AVALOS</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
     <t>CHIMALHUA</t>
   </si>
   <si>
@@ -181,46 +178,46 @@
     <t>ANETTE</t>
   </si>
   <si>
-    <t>GIOVANNI</t>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
   </si>
   <si>
     <t>SALMA AISHA</t>
@@ -1213,7 +1210,7 @@
         <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1227,7 +1224,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920284</v>
+        <v>22330051920053</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1236,13 +1233,13 @@
         <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1250,7 +1247,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920333</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1259,7 +1256,7 @@
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1273,16 +1270,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920053</v>
+        <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1296,16 +1293,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920061</v>
+        <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1319,16 +1316,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920068</v>
+        <v>21330051920053</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1342,16 +1339,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920053</v>
+        <v>22330051920084</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1365,22 +1362,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920084</v>
+        <v>22330051920189</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1388,16 +1385,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920189</v>
+        <v>22330051920043</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1411,22 +1408,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920043</v>
+        <v>22330051920352</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1434,45 +1431,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920352</v>
+        <v>22330051920173</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920173</v>
+        <v>22330051920114</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1480,16 +1477,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920114</v>
+        <v>22330051920122</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1503,22 +1500,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920122</v>
+        <v>22330051920157</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1526,22 +1523,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920157</v>
+        <v>22330051920333</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1552,13 +1549,13 @@
         <v>22330051920062</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1578,10 +1575,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1601,10 +1598,10 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -82,151 +82,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>AYOHUA</t>
   </si>
   <si>
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER</t>
   </si>
   <si>
     <t>JIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>ALEXANDRA</t>
   </si>
 </sst>
 </file>
@@ -1020,16 +927,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1046,13 +953,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>97.62</v>
       </c>
       <c r="H3">
         <v>8.199999999999999</v>
@@ -1072,16 +979,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>86.11</v>
+        <v>88.89</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1098,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>69.77</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H5">
         <v>7.2</v>
@@ -1124,16 +1031,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1150,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7">
-        <v>92.11</v>
+        <v>97.37</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1169,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1201,16 +1108,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1224,16 +1131,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920053</v>
+        <v>22330051920079</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1247,16 +1154,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920061</v>
+        <v>22330051920084</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1270,30 +1177,30 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920212</v>
+        <v>22330051920157</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920068</v>
+        <v>22330051920333</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1302,7 +1209,7 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1311,21 +1218,21 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920053</v>
+        <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1334,282 +1241,6 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920084</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920189</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920043</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920352</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920173</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920122</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920157</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920333</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920062</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920064</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920081</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
@@ -936,7 +936,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -962,7 +962,7 @@
         <v>97.62</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -988,7 +988,7 @@
         <v>88.89</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1014,7 +1014,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1040,7 +1040,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1066,7 +1066,7 @@
         <v>97.37</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20231.xlsx
@@ -936,7 +936,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -962,7 +962,7 @@
         <v>97.62</v>
       </c>
       <c r="H3">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -988,7 +988,7 @@
         <v>88.89</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1014,7 +1014,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1040,7 +1040,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1066,7 +1066,7 @@
         <v>97.37</v>
       </c>
       <c r="H7">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
